--- a/reports/Debug-snowbowl-20260106/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260106/For Winter Ending (Actual)_Revenue.xlsx
@@ -55,19 +55,19 @@
     <t>account</t>
   </si>
   <si>
+    <t xml:space="preserve">T101                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T104                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T257                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T101                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T104                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T257                     </t>
   </si>
   <si>
     <t>department</t>
@@ -495,26 +495,26 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="2">
-        <v>379509.6400</v>
+        <v>-4682.4200</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2">
-        <v>-4682.4200</v>
+        <v>243.1000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -528,7 +528,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>243.1000</v>
+        <v>-2.9500</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -542,7 +542,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>-2.9500</v>
+        <v>4943014.5100</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -556,7 +556,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>4943014.5100</v>
+        <v>348.0400</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -570,7 +570,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>348.0400</v>
+        <v>379509.6400</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -654,7 +654,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="2">
-        <v>877111.8800</v>
+        <v>877133.3800</v>
       </c>
     </row>
     <row r="15" spans="1:4">
